--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.6メッセージ管理方式.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.6メッセージ管理方式.xlsx
@@ -1,24 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD15B0F-8734-4A53-87A7-17AA270CD1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A0628E-9F93-4E71-BE26-0554E82B9BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.6.メッセージ管理方式" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'7.6.メッセージ管理方式'!$A$1:$AI$37</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'7.6.メッセージ管理方式'!$A$1:$AI$37</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'7.6.メッセージ管理方式'!$A$1:$AI$37</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'7.6.メッセージ管理方式'!$A$1:$AI$37</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'7.6.メッセージ管理方式'!$A$1:$AI$37</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <si>
+    <t>プロジェクト名</t>
+    <phoneticPr fontId="3"/>
+  </si>
   <si>
     <t>工程</t>
     <rPh sb="0" eb="2">
@@ -42,6 +44,16 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>要件定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>作成</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -72,6 +84,145 @@
   </si>
   <si>
     <t>処理方式共通</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージ管理方式</t>
+  </si>
+  <si>
+    <t>基本方針</t>
+  </si>
+  <si>
+    <t>メッセージ管理の概要</t>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Nablarchで提供されるメッセージ管理機能を使用して、メッセージの一元管理を実現する。</t>
+    <rPh sb="19" eb="21">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジツゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本節で取り扱うメッセージには、ユーザに通知するメッセージ(エラーメッセージ、インフォメーションメッセージ等)および、</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>障害発生時に運用担当者に通知するメッセージ(障害通知ログと障害解析ログのメッセージ)が含まれる。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユーザに通知するメッセージはメッセージID、障害発生時に運用担当者に通知するメッセージは障害コードにより識別される。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージID、障害コードのID体系については、【ID体系】を参照。</t>
+    <rPh sb="31" eb="33">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージの定義場所</t>
+    <rPh sb="6" eb="8">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージの定義場所としては、プロパティファイルを採用する。</t>
+    <rPh sb="6" eb="10">
+      <t>テイギバショ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、Javaのプロパティファイルでメッセージを定義し、リソースとしてアプリケーション内部に組み込んで使用する方式となる。</t>
+    <rPh sb="25" eb="27">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージのロード方式</t>
+    <rPh sb="9" eb="11">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージのロードの概要</t>
+    <rPh sb="10" eb="12">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Nablarchメッセージ管理機能では、メッセージをメモリ上でキャッシュすることで、メッセージの取得処理を高速化する。</t>
+    <rPh sb="29" eb="30">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>コウソクカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なお、キャッシュしたメッセージは、アプリケーションを再起動するまで最新化できない。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ロード手段</t>
+    <rPh sb="3" eb="5">
+      <t>シュダン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手段</t>
+    <rPh sb="0" eb="2">
+      <t>シュダン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -82,196 +233,67 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>メッセージ管理方式</t>
-  </si>
-  <si>
-    <t>基本方針</t>
-  </si>
-  <si>
-    <t>メッセージのロード方式</t>
+    <t>一括ロード方式</t>
+  </si>
+  <si>
+    <t>パフォーマンスの向上が期待できるため。</t>
+  </si>
+  <si>
+    <t>オンデマンドロード方式</t>
+  </si>
+  <si>
+    <t>バッチ機能では、特定のメッセージのみを繰り返し使用する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そのため、起動時に一括ロードは行わず、初回の取得要求時にロードを行うことで、</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャッシュの容量が圧迫されず、パフォーマンスの向上が期待できるため。</t>
+  </si>
+  <si>
+    <t>画面処理方式</t>
+    <rPh sb="0" eb="6">
+      <t>ガメンショリホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力処理方式(REST)</t>
+    <rPh sb="0" eb="6">
+      <t>ニュウリョクショリホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バッチ処理方式</t>
+    <rPh sb="3" eb="7">
+      <t>ショリホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そのため、起動時に一度だけすべてのメッセージをキャッシュにロードしておけば、</t>
     <rPh sb="9" eb="11">
-      <t>ホウシキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>メッセージの定義場所</t>
-    <rPh sb="6" eb="8">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>メッセージ管理の概要</t>
-    <rPh sb="5" eb="7">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>プロジェクト名</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>メッセージのロードの概要</t>
-    <rPh sb="10" eb="12">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Nablarchメッセージ管理機能では、メッセージをメモリ上でキャッシュすることで、メッセージの取得処理を高速化する。</t>
-    <rPh sb="29" eb="30">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>コウソクカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>対象</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>手段</t>
-    <rPh sb="0" eb="2">
-      <t>シュダン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>オンデマンドロード方式</t>
-  </si>
-  <si>
-    <t>オンライン機能</t>
-  </si>
-  <si>
-    <t>バッチ機能</t>
-    <rPh sb="3" eb="5">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ロード手段</t>
-    <rPh sb="3" eb="5">
-      <t>シュダン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一括ロード方式</t>
-  </si>
-  <si>
-    <t>なお、キャッシュしたメッセージは、アプリケーションを再起動するまで最新化できない。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ユーザに通知するメッセージはメッセージID、障害発生時に運用担当者に通知するメッセージは障害コードにより識別される。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Nablarchで提供されるメッセージ管理機能を使用して、メッセージの一元管理を実現する。</t>
-    <rPh sb="19" eb="21">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ジツゲン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>障害発生時に運用担当者に通知するメッセージ(障害通知ログと障害解析ログのメッセージ)が含まれる。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>バッチ機能では、特定のメッセージのみを繰り返し使用する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>そのため、起動時に一括ロードは行わず、初回の取得要求時にロードを行うことで、</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>キャッシュの容量が圧迫されず、パフォーマンスの向上が期待できるため。</t>
-  </si>
-  <si>
-    <t>オンライン機能では、メッセージ全体の大部分が使用される。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>そのため、起動時にすべてのメッセージをキャッシュにロードしておけば、</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>起動中に新たにメッセージのロードを行う必要がなくなり、</t>
-  </si>
-  <si>
-    <t>パフォーマンスの向上が期待できるため。</t>
-  </si>
-  <si>
-    <t>本節で取り扱うメッセージには、ユーザに通知するメッセージ(エラーメッセージ、インフォメーションメッセージ等)および、</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>メッセージID、障害コードのID体系については、【ID体系】を参照。</t>
-    <rPh sb="31" eb="33">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>要件定義</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>メッセージの定義場所としては、プロパティファイルを採用する。</t>
-    <rPh sb="6" eb="10">
-      <t>テイギバショ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>サイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>これは、Javaのプロパティファイルでメッセージを定義し、リソースとしてアプリケーション内部に組み込んで使用する方式となる。</t>
-    <rPh sb="25" eb="27">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ナイブ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>シヨウ</t>
+      <t>イチド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>各リクエストごとにメッセージのロードを行う必要がなくなり、</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>画面処理方式および入力処理方式(REST)では、一度起動したプロセスが常駐し処理を行う。</t>
+    <rPh sb="0" eb="6">
+      <t>ガメンショリホウシキ</t>
+    </rPh>
+    <rPh sb="9" eb="15">
+      <t>ニュウリョクショリホウシキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -495,50 +517,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -556,70 +578,55 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -640,23 +647,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -676,7 +674,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1020,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI451"/>
@@ -1033,142 +1031,142 @@
   <sheetData>
     <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="44"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="39"/>
       <c r="P1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="47"/>
+      <c r="R1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="42"/>
       <c r="Y1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="41"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="44"/>
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="36"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="53"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="39"/>
       <c r="P2" s="8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="56"/>
+      <c r="R2" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="48"/>
       <c r="Y2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="41"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="36"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="59"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="51"/>
       <c r="Y3" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="41"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="36"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1178,7 +1176,7 @@
         <v>7.6.</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1188,7 +1186,7 @@
         <v>7.6.1.</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1198,44 +1196,43 @@
         <v>7.6.1.1.</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="4" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O15" s="25"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D16" s="15"/>
@@ -1248,22 +1245,22 @@
         <v>7.6.1.2.</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E18" s="15"/>
       <c r="F18" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E19" s="15"/>
       <c r="F19" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
     </row>
@@ -1273,23 +1270,23 @@
         <v>7.6.2.</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D22" s="15"/>
-      <c r="E22" s="24" t="str">
+      <c r="E22" s="22" t="str">
         <f>$D$21&amp;"1."</f>
         <v>7.6.2.1.</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D23" s="15"/>
       <c r="F23" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1298,7 +1295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D25" s="15"/>
     </row>
     <row r="26" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1307,29 +1304,29 @@
         <v>7.6.2.2.</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E27" s="15"/>
     </row>
     <row r="28" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F28" s="16" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
       <c r="K28" s="16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
       <c r="O28" s="18"/>
       <c r="P28" s="17" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
@@ -1352,281 +1349,157 @@
     </row>
     <row r="29" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
-      <c r="AD29" s="26"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="26"/>
-      <c r="AG29" s="26"/>
-      <c r="AH29" s="27"/>
+        <v>37</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH29" s="23"/>
     </row>
     <row r="30" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="26"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="26"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="26"/>
-      <c r="AC30" s="26"/>
-      <c r="AD30" s="26"/>
-      <c r="AE30" s="26"/>
-      <c r="AF30" s="26"/>
-      <c r="AG30" s="26"/>
-      <c r="AH30" s="27"/>
+      <c r="F30" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="28"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH30" s="23"/>
     </row>
     <row r="31" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="26" t="s">
+      <c r="K31" s="28"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH31" s="23"/>
+    </row>
+    <row r="32" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="21"/>
+      <c r="W32" s="21"/>
+      <c r="X32" s="21"/>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="21"/>
+      <c r="AA32" s="21"/>
+      <c r="AB32" s="21"/>
+      <c r="AC32" s="21"/>
+      <c r="AD32" s="21"/>
+      <c r="AE32" s="21"/>
+      <c r="AF32" s="21"/>
+      <c r="AG32" s="21"/>
+      <c r="AH32" s="24"/>
+    </row>
+    <row r="33" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F33" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH33" s="23"/>
+    </row>
+    <row r="34" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F34" s="19"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
-      <c r="AD31" s="26"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="26"/>
-      <c r="AG31" s="26"/>
-      <c r="AH31" s="27"/>
-    </row>
-    <row r="32" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F32" s="21"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="28" t="s">
+      <c r="AH34" s="23"/>
+    </row>
+    <row r="35" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F35" s="19"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
-      <c r="AE32" s="28"/>
-      <c r="AF32" s="28"/>
-      <c r="AG32" s="28"/>
-      <c r="AH32" s="29"/>
-    </row>
-    <row r="33" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F33" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="26"/>
-      <c r="AD33" s="26"/>
-      <c r="AE33" s="26"/>
-      <c r="AF33" s="26"/>
-      <c r="AG33" s="26"/>
-      <c r="AH33" s="27"/>
-    </row>
-    <row r="34" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F34" s="23"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
-      <c r="AA34" s="26"/>
-      <c r="AB34" s="26"/>
-      <c r="AC34" s="26"/>
-      <c r="AD34" s="26"/>
-      <c r="AE34" s="26"/>
-      <c r="AF34" s="26"/>
-      <c r="AG34" s="26"/>
-      <c r="AH34" s="27"/>
-    </row>
-    <row r="35" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F35" s="23"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="26"/>
-      <c r="AD35" s="26"/>
-      <c r="AE35" s="26"/>
-      <c r="AF35" s="26"/>
-      <c r="AG35" s="26"/>
-      <c r="AH35" s="27"/>
+      <c r="AH35" s="23"/>
     </row>
     <row r="36" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F36" s="21"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="37"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
-      <c r="AD36" s="28"/>
-      <c r="AE36" s="28"/>
-      <c r="AF36" s="28"/>
-      <c r="AG36" s="28"/>
-      <c r="AH36" s="29"/>
-    </row>
-    <row r="37" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F36" s="20"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+      <c r="AH36" s="24"/>
+    </row>
+    <row r="37" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D37" s="15"/>
     </row>
-    <row r="38" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="42" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="43" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="44" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
